--- a/data/pack/us/colza.xlsx
+++ b/data/pack/us/colza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K229"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13029,6 +13029,61 @@
         </is>
       </c>
       <c r="K229" t="inlineStr">
+        <is>
+          <t>Source: USDA National Agricultural Statistics Service (NASS), Quick Stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>colza</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Colza</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>USDA National Agricultural Statistics Service (Quick Stats)</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
         <is>
           <t>Source: USDA National Agricultural Statistics Service (NASS), Quick Stats</t>
         </is>
@@ -13128,7 +13183,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13194,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -13234,7 +13289,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
